--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5601.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5601.xlsx
@@ -1016,6 +1016,9 @@
       <c r="D10" t="n">
         <v>1.02</v>
       </c>
+      <c r="H10" t="n">
+        <v>0.57</v>
+      </c>
       <c r="I10" t="n">
         <v>0.675</v>
       </c>
@@ -1037,12 +1040,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: N1@DRIVE, N2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5601-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: N1@DRIVE, N2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5601-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5601-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5601-06-06-06-FG (PARTcommunity / CADENAS, N1@DRIVE=N3, N2@DRIVE=N2, THDMAJ_A1@DRIVE=ATHD, THDMAJ_A2@DRIVE=ATHD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5601-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5601-06-06-06-FG (PARTcommunity / CADENAS, N1@DRIVE=N3, N2@DRIVE=N2, THDMAJ_A1@DRIVE=ATHD, THDMAJ_A2@DRIVE=ATHD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1150,6 +1153,9 @@
       <c r="D12" t="n">
         <v>2.08</v>
       </c>
+      <c r="H12" t="n">
+        <v>1.72</v>
+      </c>
       <c r="I12" t="n">
         <v>1.9</v>
       </c>
@@ -1171,12 +1177,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: N1@DRIVE, N2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: N1@DRIVE, N2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 5601-24-24-24-FG (PARTcommunity / CADENAS, N1@DRIVE=N3, N2@DRIVE=N2, THDMAJ_A1@DRIVE=ATHD, THDMAJ_A2@DRIVE=ATHD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 5601-24-24-24-FG (PARTcommunity / CADENAS, N1@DRIVE=N3, N2@DRIVE=N2, THDMAJ_A1@DRIVE=ATHD, THDMAJ_A2@DRIVE=ATHD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">

--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5601.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5601.xlsx
@@ -1010,12 +1010,24 @@
           <t>5601-06-06-06-FG</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>1.22</v>
+      </c>
       <c r="C10" t="n">
         <v>1.22</v>
       </c>
       <c r="D10" t="n">
         <v>1.02</v>
       </c>
+      <c r="E10" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.406</v>
+      </c>
       <c r="H10" t="n">
         <v>0.57</v>
       </c>
@@ -1035,17 +1047,17 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: N1@DRIVE, N2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5601-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: N1@DRIVE, N2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, N_1@DRIVE, W@HEX, D1@BORE, D2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5601-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5601-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5601-06-06-06-FG (PARTcommunity / CADENAS, N1@DRIVE=N3, N2@DRIVE=N2, THDMAJ_A1@DRIVE=ATHD, THDMAJ_A2@DRIVE=ATHD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5601-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5601-06-06-06-FG (PARTcommunity / CADENAS, N1@DRIVE=N3, N2@DRIVE=N2, THDMAJ_A1@DRIVE=ATHD, THDMAJ_A2@DRIVE=ATHD, THDMAJ_A3@DRIVE=ATHD, N_1@DRIVE=N1, W@HEX=Y, D1@BORE=A1D, D2@BORE=A2D; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1147,12 +1159,24 @@
           <t>5601-24-24-24-FG</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>2.64</v>
+      </c>
       <c r="C12" t="n">
         <v>2.64</v>
       </c>
       <c r="D12" t="n">
         <v>2.08</v>
       </c>
+      <c r="E12" t="n">
+        <v>2.562</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.5</v>
+      </c>
       <c r="H12" t="n">
         <v>1.72</v>
       </c>
@@ -1172,17 +1196,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: N1@DRIVE, N2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: N1@DRIVE, N2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, N_1@DRIVE, W@HEX, D1@BORE, D2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 5601-24-24-24-FG (PARTcommunity / CADENAS, N1@DRIVE=N3, N2@DRIVE=N2, THDMAJ_A1@DRIVE=ATHD, THDMAJ_A2@DRIVE=ATHD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 5601-24-24-24-FG (PARTcommunity / CADENAS, N1@DRIVE=N3, N2@DRIVE=N2, THDMAJ_A1@DRIVE=ATHD, THDMAJ_A2@DRIVE=ATHD, THDMAJ_A3@DRIVE=ATHD, N_1@DRIVE=N1, W@HEX=Y, D1@BORE=A1D, D2@BORE=A2D; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
